--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:43:27+00:00</t>
+    <t>2026-07-01T12:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:03:19+00:00</t>
+    <t>2026-07-03T07:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1136,7 +1136,7 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260420150250</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationInterpretation-cisis|20260619134042</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1222,7 +1222,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260420150249</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ObservationMethod-cisis|20260619134042</t>
   </si>
   <si>
     <t>OBX-17</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T07:33:59+00:00</t>
+    <t>2026-07-08T09:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
+++ b/feat/migration-contenu-fhir/ig/StructureDefinition-fr-observation-transfusion-accidents-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T09:43:12+00:00</t>
+    <t>2026-07-08T10:07:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
